--- a/data/spring_data.xlsx
+++ b/data/spring_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH21"/>
+  <dimension ref="A1:AG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,120 +469,115 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>泥水状况</t>
+          <t>液温</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>液温</t>
+          <t>DO(mg/L)</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>DO(mg/L)</t>
+          <t>NaCl(mg/L)</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>NaCl(mg/L)</t>
+          <t>电导率(us/cm)</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>电导率(us/cm)</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>TOC（mg/L)</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>TOC（mg/L)</t>
+          <t>TC(mg/L)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>TC(mg/L)</t>
+          <t>IC(mg/L)</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>IC(mg/L)</t>
+          <t>总氮（mg/L)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>总氮（mg/L)</t>
+          <t>总磷（mg/L)</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>总磷（mg/L)</t>
+          <t>铵态氮（mg/L)</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>铵态氮（mg/L)</t>
+          <t>硝态氮（mg/L)</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>硝态氮（mg/L)</t>
+          <t>COD（mg/L)</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>COD（mg/L)</t>
+          <t>固总碳（g/kg)</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>固总碳（g/kg)</t>
+          <t>DOC(mg/kg)</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>DOC(mg/kg)</t>
+          <t>全磷（g/kg)</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>全磷（g/kg)</t>
+          <t>有机碳（g/kg)</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>有机碳（g/kg)</t>
+          <t>无机碳（g/kg)</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>无机碳（g/kg)</t>
+          <t>（固）铵态氮（mg/kg）</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>（固）铵态氮（mg/kg）</t>
+          <t>（固）硝态氮（mg/kg）</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>（固）硝态氮（mg/kg）</t>
+          <t>采样时间</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>采样时间</t>
+          <t>采样时段</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
-        <is>
-          <t>采样时段</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
         <is>
           <t>季节</t>
         </is>
@@ -621,11 +616,7 @@
       <c r="J2" t="n">
         <v>17</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -645,16 +636,15 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="n">
+      <c r="AE2" t="n">
         <v>4.1</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>11:02:00</t>
+        </is>
+      </c>
       <c r="AG2" t="inlineStr">
-        <is>
-          <t>11:02:00</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -693,66 +683,61 @@
       <c r="J3" t="n">
         <v>17</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K3" t="n">
+        <v>16.9</v>
       </c>
       <c r="L3" t="n">
-        <v>16.9</v>
+        <v>5.28</v>
       </c>
       <c r="M3" t="n">
-        <v>5.28</v>
+        <v>651</v>
       </c>
       <c r="N3" t="n">
-        <v>651</v>
+        <v>1102</v>
       </c>
       <c r="O3" t="n">
-        <v>1102</v>
+        <v>8.32</v>
       </c>
       <c r="P3" t="n">
-        <v>8.32</v>
+        <v>49.272</v>
       </c>
       <c r="Q3" t="n">
-        <v>49.272</v>
+        <v>123.42</v>
       </c>
       <c r="R3" t="n">
-        <v>123.42</v>
+        <v>74.16</v>
       </c>
       <c r="S3" t="n">
-        <v>74.16</v>
+        <v>76.25</v>
       </c>
       <c r="T3" t="n">
-        <v>76.25</v>
+        <v>5.08</v>
       </c>
       <c r="U3" t="n">
-        <v>5.08</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>70.76000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="W3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X3" t="n">
         <v>65.65000000000001</v>
       </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="n">
+      <c r="AE3" t="n">
         <v>4.1</v>
       </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
       <c r="AG3" t="inlineStr">
-        <is>
-          <t>10:25:00</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -791,66 +776,61 @@
       <c r="J4" t="n">
         <v>17</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K4" t="n">
+        <v>17.5</v>
       </c>
       <c r="L4" t="n">
-        <v>17.5</v>
+        <v>3.96</v>
       </c>
       <c r="M4" t="n">
-        <v>3.96</v>
+        <v>394</v>
       </c>
       <c r="N4" t="n">
-        <v>394</v>
+        <v>648</v>
       </c>
       <c r="O4" t="n">
-        <v>648</v>
+        <v>7.74</v>
       </c>
       <c r="P4" t="n">
-        <v>7.74</v>
+        <v>29.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>29.35</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>70.09999999999999</v>
+        <v>40.75</v>
       </c>
       <c r="S4" t="n">
-        <v>40.75</v>
+        <v>22.21</v>
       </c>
       <c r="T4" t="n">
-        <v>22.21</v>
+        <v>2.19</v>
       </c>
       <c r="U4" t="n">
-        <v>2.19</v>
+        <v>17.68</v>
       </c>
       <c r="V4" t="n">
-        <v>17.68</v>
+        <v>0.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="X4" t="n">
         <v>31.78</v>
       </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="n">
+      <c r="AE4" t="n">
         <v>4.1</v>
       </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>10:07:00</t>
+        </is>
+      </c>
       <c r="AG4" t="inlineStr">
-        <is>
-          <t>10:07:00</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -889,11 +869,7 @@
       <c r="J5" t="n">
         <v>16</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>无水有泥</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -906,37 +882,36 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>95.2694034576416</v>
+      </c>
       <c r="Y5" t="n">
-        <v>95.2694034576416</v>
+        <v>151.789012234385</v>
       </c>
       <c r="Z5" t="n">
-        <v>151.789012234385</v>
+        <v>1.54</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.54</v>
+        <v>35.7196414406254</v>
       </c>
       <c r="AB5" t="n">
-        <v>35.7196414406254</v>
+        <v>8.41</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.41</v>
+        <v>3.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.9</v>
+        <v>1.13</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF5" t="n">
         <v>4.1</v>
       </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>09:52:00</t>
+        </is>
+      </c>
       <c r="AG5" t="inlineStr">
-        <is>
-          <t>09:52:00</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -975,11 +950,7 @@
       <c r="J6" t="n">
         <v>16</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -999,16 +970,15 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="n">
+      <c r="AE6" t="n">
         <v>4.1</v>
       </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>09:40:00</t>
+        </is>
+      </c>
       <c r="AG6" t="inlineStr">
-        <is>
-          <t>09:40:00</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -1047,11 +1017,7 @@
       <c r="J7" t="n">
         <v>12</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1071,16 +1037,15 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="n">
+      <c r="AE7" t="n">
         <v>4.1</v>
       </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
       <c r="AG7" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -1119,66 +1084,61 @@
       <c r="J8" t="n">
         <v>15</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K8" t="n">
+        <v>15.4</v>
       </c>
       <c r="L8" t="n">
-        <v>15.4</v>
+        <v>3.72</v>
       </c>
       <c r="M8" t="n">
-        <v>3.72</v>
+        <v>534</v>
       </c>
       <c r="N8" t="n">
-        <v>534</v>
+        <v>888</v>
       </c>
       <c r="O8" t="n">
-        <v>888</v>
+        <v>7.51</v>
       </c>
       <c r="P8" t="n">
-        <v>7.51</v>
+        <v>29.826</v>
       </c>
       <c r="Q8" t="n">
-        <v>29.826</v>
+        <v>109.5</v>
       </c>
       <c r="R8" t="n">
-        <v>109.5</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>79.68000000000001</v>
+        <v>45.28</v>
       </c>
       <c r="T8" t="n">
-        <v>45.28</v>
+        <v>3.92</v>
       </c>
       <c r="U8" t="n">
-        <v>3.92</v>
+        <v>42.08</v>
       </c>
       <c r="V8" t="n">
-        <v>42.08</v>
+        <v>0.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="X8" t="n">
         <v>26.18</v>
       </c>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="n">
+      <c r="AE8" t="n">
         <v>4.1</v>
       </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>09:20:00</t>
+        </is>
+      </c>
       <c r="AG8" t="inlineStr">
-        <is>
-          <t>09:20:00</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -1217,66 +1177,61 @@
       <c r="J9" t="n">
         <v>16</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K9" t="n">
+        <v>15</v>
       </c>
       <c r="L9" t="n">
-        <v>15</v>
+        <v>2.89</v>
       </c>
       <c r="M9" t="n">
-        <v>2.89</v>
+        <v>345</v>
       </c>
       <c r="N9" t="n">
-        <v>345</v>
+        <v>572</v>
       </c>
       <c r="O9" t="n">
-        <v>572</v>
+        <v>7.18</v>
       </c>
       <c r="P9" t="n">
-        <v>7.18</v>
+        <v>20.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>20.25</v>
+        <v>82.39</v>
       </c>
       <c r="R9" t="n">
-        <v>82.39</v>
+        <v>62.14</v>
       </c>
       <c r="S9" t="n">
-        <v>62.14</v>
+        <v>6.96</v>
       </c>
       <c r="T9" t="n">
-        <v>6.96</v>
+        <v>1.14</v>
       </c>
       <c r="U9" t="n">
-        <v>1.14</v>
+        <v>4.81</v>
       </c>
       <c r="V9" t="n">
-        <v>4.81</v>
+        <v>0.08</v>
       </c>
       <c r="W9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="X9" t="n">
         <v>16.39</v>
       </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="n">
+      <c r="AE9" t="n">
         <v>4.2</v>
       </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
       <c r="AG9" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -1315,66 +1270,61 @@
       <c r="J10" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K10" t="n">
+        <v>17.8</v>
       </c>
       <c r="L10" t="n">
-        <v>17.8</v>
+        <v>7.27</v>
       </c>
       <c r="M10" t="n">
-        <v>7.27</v>
+        <v>330</v>
       </c>
       <c r="N10" t="n">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="O10" t="n">
-        <v>580</v>
+        <v>7.57</v>
       </c>
       <c r="P10" t="n">
-        <v>7.57</v>
+        <v>15.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.04</v>
+        <v>74.97</v>
       </c>
       <c r="R10" t="n">
-        <v>74.97</v>
+        <v>59.93</v>
       </c>
       <c r="S10" t="n">
-        <v>59.93</v>
+        <v>13.62</v>
       </c>
       <c r="T10" t="n">
-        <v>13.62</v>
+        <v>0.67</v>
       </c>
       <c r="U10" t="n">
-        <v>0.67</v>
+        <v>8.56</v>
       </c>
       <c r="V10" t="n">
-        <v>8.56</v>
+        <v>3.41</v>
       </c>
       <c r="W10" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="X10" t="n">
         <v>14.06</v>
       </c>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="n">
+      <c r="AE10" t="n">
         <v>4.2</v>
       </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
       <c r="AG10" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -1413,11 +1363,7 @@
       <c r="J11" t="n">
         <v>16</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1437,16 +1383,15 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="n">
+      <c r="AE11" t="n">
         <v>4.2</v>
       </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>10:45:00</t>
+        </is>
+      </c>
       <c r="AG11" t="inlineStr">
-        <is>
-          <t>10:45:00</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -1485,11 +1430,7 @@
       <c r="J12" t="n">
         <v>17</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1509,16 +1450,15 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="n">
+      <c r="AE12" t="n">
         <v>4.2</v>
       </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
       <c r="AG12" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -1557,11 +1497,7 @@
       <c r="J13" t="n">
         <v>16</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1581,16 +1517,15 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="n">
+      <c r="AE13" t="n">
         <v>4.8</v>
       </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>09:30:00</t>
+        </is>
+      </c>
       <c r="AG13" t="inlineStr">
-        <is>
-          <t>09:30:00</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -1629,66 +1564,61 @@
       <c r="J14" t="n">
         <v>15</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K14" t="n">
+        <v>17.7</v>
       </c>
       <c r="L14" t="n">
-        <v>17.7</v>
+        <v>0.95</v>
       </c>
       <c r="M14" t="n">
-        <v>0.95</v>
+        <v>503</v>
       </c>
       <c r="N14" t="n">
-        <v>503</v>
+        <v>872</v>
       </c>
       <c r="O14" t="n">
-        <v>872</v>
+        <v>6.48</v>
       </c>
       <c r="P14" t="n">
-        <v>6.48</v>
+        <v>40.452</v>
       </c>
       <c r="Q14" t="n">
-        <v>40.452</v>
+        <v>98.52</v>
       </c>
       <c r="R14" t="n">
-        <v>98.52</v>
+        <v>58.074</v>
       </c>
       <c r="S14" t="n">
-        <v>58.074</v>
+        <v>16.93</v>
       </c>
       <c r="T14" t="n">
-        <v>16.93</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>3.34</v>
+        <v>8.99</v>
       </c>
       <c r="V14" t="n">
-        <v>8.99</v>
+        <v>0.04</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="X14" t="n">
         <v>36.28</v>
       </c>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="n">
+      <c r="AE14" t="n">
         <v>4.8</v>
       </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>09:45:00</t>
+        </is>
+      </c>
       <c r="AG14" t="inlineStr">
-        <is>
-          <t>09:45:00</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -1697,7 +1627,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R14(溢出)</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1727,66 +1657,61 @@
       <c r="J15" t="n">
         <v>15</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K15" t="n">
+        <v>19.3</v>
       </c>
       <c r="L15" t="n">
-        <v>19.3</v>
+        <v>4.88</v>
       </c>
       <c r="M15" t="n">
-        <v>4.88</v>
+        <v>428</v>
       </c>
       <c r="N15" t="n">
-        <v>428</v>
+        <v>773</v>
       </c>
       <c r="O15" t="n">
-        <v>773</v>
+        <v>6.81</v>
       </c>
       <c r="P15" t="n">
-        <v>6.81</v>
+        <v>39.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>39.21</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>77.06999999999999</v>
+        <v>37.86</v>
       </c>
       <c r="S15" t="n">
-        <v>37.86</v>
+        <v>5.01</v>
       </c>
       <c r="T15" t="n">
-        <v>5.01</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>1.74</v>
+        <v>0.06</v>
       </c>
       <c r="V15" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X15" t="n">
         <v>58.81</v>
       </c>
+      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="n">
+      <c r="AE15" t="n">
         <v>4.8</v>
       </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
       <c r="AG15" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -1825,11 +1750,7 @@
       <c r="J16" t="n">
         <v>16</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>无水有泥</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -1842,37 +1763,36 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="n">
+        <v>299.455604553223</v>
+      </c>
       <c r="Y16" t="n">
-        <v>299.455604553223</v>
+        <v>6513.92850797872</v>
       </c>
       <c r="Z16" t="n">
-        <v>6513.92850797872</v>
+        <v>2.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.67</v>
+        <v>205.90521188175</v>
       </c>
       <c r="AB16" t="n">
-        <v>205.90521188175</v>
+        <v>9.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.15</v>
+        <v>953.79</v>
       </c>
       <c r="AD16" t="n">
-        <v>953.79</v>
+        <v>1.39</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF16" t="n">
         <v>4.8</v>
       </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
       <c r="AG16" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -1911,66 +1831,61 @@
       <c r="J17" t="n">
         <v>17</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K17" t="n">
+        <v>16.2</v>
       </c>
       <c r="L17" t="n">
-        <v>16.2</v>
+        <v>3.35</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>608</v>
       </c>
       <c r="N17" t="n">
-        <v>608</v>
+        <v>1015</v>
       </c>
       <c r="O17" t="n">
-        <v>1015</v>
+        <v>8.74</v>
       </c>
       <c r="P17" t="n">
-        <v>8.74</v>
+        <v>106.2</v>
       </c>
       <c r="Q17" t="n">
+        <v>203.28</v>
+      </c>
+      <c r="R17" t="n">
+        <v>97.02</v>
+      </c>
+      <c r="S17" t="n">
+        <v>124.82</v>
+      </c>
+      <c r="T17" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="U17" t="n">
+        <v>103.68</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="W17" t="n">
         <v>106.2</v>
       </c>
-      <c r="R17" t="n">
-        <v>203.28</v>
-      </c>
-      <c r="S17" t="n">
-        <v>97.02</v>
-      </c>
-      <c r="T17" t="n">
-        <v>124.82</v>
-      </c>
-      <c r="U17" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="V17" t="n">
-        <v>103.68</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="X17" t="n">
-        <v>106.2</v>
-      </c>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="n">
+      <c r="AE17" t="n">
         <v>4.8</v>
       </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
       <c r="AG17" t="inlineStr">
-        <is>
-          <t>14:30:00</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -2009,11 +1924,7 @@
       <c r="J18" t="n">
         <v>17</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2033,16 +1944,15 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="n">
+      <c r="AE18" t="n">
         <v>4.8</v>
       </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>14:50:00</t>
+        </is>
+      </c>
       <c r="AG18" t="inlineStr">
-        <is>
-          <t>14:50:00</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -2081,66 +1991,61 @@
       <c r="J19" t="n">
         <v>16</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K19" t="n">
+        <v>20.3</v>
       </c>
       <c r="L19" t="n">
-        <v>20.3</v>
+        <v>2.87</v>
       </c>
       <c r="M19" t="n">
-        <v>2.87</v>
+        <v>379</v>
       </c>
       <c r="N19" t="n">
-        <v>379</v>
+        <v>753</v>
       </c>
       <c r="O19" t="n">
-        <v>753</v>
+        <v>6.52</v>
       </c>
       <c r="P19" t="n">
-        <v>6.52</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>72.18000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="R19" t="n">
-        <v>97.8</v>
+        <v>25.614</v>
       </c>
       <c r="S19" t="n">
-        <v>25.614</v>
+        <v>30.97</v>
       </c>
       <c r="T19" t="n">
-        <v>30.97</v>
+        <v>7.03</v>
       </c>
       <c r="U19" t="n">
-        <v>7.03</v>
+        <v>13.33</v>
       </c>
       <c r="V19" t="n">
-        <v>13.33</v>
+        <v>0.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="X19" t="n">
         <v>522.47</v>
       </c>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="n">
+      <c r="AE19" t="n">
         <v>4.8</v>
       </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>10:33:00</t>
+        </is>
+      </c>
       <c r="AG19" t="inlineStr">
-        <is>
-          <t>10:33:00</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -2179,66 +2084,61 @@
       <c r="J20" t="n">
         <v>16</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K20" t="n">
+        <v>16.3</v>
       </c>
       <c r="L20" t="n">
-        <v>16.3</v>
+        <v>6.83</v>
       </c>
       <c r="M20" t="n">
-        <v>6.83</v>
+        <v>588</v>
       </c>
       <c r="N20" t="n">
-        <v>588</v>
+        <v>988</v>
       </c>
       <c r="O20" t="n">
-        <v>988</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>8.789999999999999</v>
+        <v>65.52</v>
       </c>
       <c r="Q20" t="n">
-        <v>65.52</v>
+        <v>132.96</v>
       </c>
       <c r="R20" t="n">
-        <v>132.96</v>
+        <v>67.44</v>
       </c>
       <c r="S20" t="n">
-        <v>67.44</v>
+        <v>98.31</v>
       </c>
       <c r="T20" t="n">
-        <v>98.31</v>
+        <v>6.62</v>
       </c>
       <c r="U20" t="n">
-        <v>6.62</v>
+        <v>89.92</v>
       </c>
       <c r="V20" t="n">
-        <v>89.92</v>
+        <v>0.67</v>
       </c>
       <c r="W20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="X20" t="n">
         <v>57.26</v>
       </c>
+      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="n">
+      <c r="AE20" t="n">
         <v>4.8</v>
       </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>11:00:00</t>
+        </is>
+      </c>
       <c r="AG20" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
@@ -2277,11 +2177,7 @@
       <c r="J21" t="n">
         <v>18</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2301,16 +2197,15 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="n">
+      <c r="AE21" t="n">
         <v>4.8</v>
       </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>15:05:00</t>
+        </is>
+      </c>
       <c r="AG21" t="inlineStr">
-        <is>
-          <t>15:05:00</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
         <is>
           <t>春季</t>
         </is>
